--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="1065">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251017120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -427,6 +427,12 @@
   </si>
   <si>
     <t>Médecine du travail (pathologie professionnelle)</t>
+  </si>
+  <si>
+    <t>083</t>
+  </si>
+  <si>
+    <t>Médecine polyvalente</t>
   </si>
   <si>
     <t>084</t>
@@ -3463,7 +3469,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7611,15 +7617,23 @@
         <v>1060</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B519" t="s" s="2">
         <v>1062</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="s" s="2">
+        <v>1063</v>
+      </c>
+      <c r="B520" t="s" s="2">
+        <v>1064</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="1065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="1073">
   <si>
     <t>Property</t>
   </si>
@@ -162,7 +162,7 @@
     <t>015</t>
   </si>
   <si>
-    <t>Centre antipoison et de toxicovigilance (CAPTV)</t>
+    <t>Conseil antipoison et toxicovigilance</t>
   </si>
   <si>
     <t>016</t>
@@ -717,12 +717,6 @@
     <t>Tabacologie</t>
   </si>
   <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>Toxicologie</t>
-  </si>
-  <si>
     <t>145</t>
   </si>
   <si>
@@ -3199,6 +3193,36 @@
   </si>
   <si>
     <t>Evaluation de la mémoire (bilan mémoire)</t>
+  </si>
+  <si>
+    <t>598</t>
+  </si>
+  <si>
+    <t>Toxicologie clinique</t>
+  </si>
+  <si>
+    <t>599</t>
+  </si>
+  <si>
+    <t>Analyse toxicologique</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>Prise en charge des malaises et surdoses liés à la prise de drogues</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>Médiation pour le maintien en hospitalisation</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Prise en charge coordonnée des patients atteints de maladies neurodégénératives</t>
   </si>
   <si>
     <t/>
@@ -3469,7 +3493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7625,15 +7649,47 @@
         <v>1062</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="s" s="2">
+        <v>1066</v>
+      </c>
+      <c r="B521" t="s" s="2">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="s" s="2">
+        <v>1068</v>
+      </c>
+      <c r="B522" t="s" s="2">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="B523" t="s" s="2">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="s" s="2">
+        <v>1071</v>
+      </c>
+      <c r="B524" t="s" s="2">
+        <v>1072</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="1075">
   <si>
     <t>Property</t>
   </si>
@@ -715,6 +715,12 @@
   </si>
   <si>
     <t>Tabacologie</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Toxicologie</t>
   </si>
   <si>
     <t>145</t>
@@ -3493,7 +3499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7681,15 +7687,23 @@
         <v>1070</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>1072</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="s" s="2">
+        <v>1073</v>
+      </c>
+      <c r="B525" t="s" s="2">
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
